--- a/artfynd/A 35673-2026 artfynd.xlsx
+++ b/artfynd/A 35673-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137360121</v>
       </c>
       <c r="B2" t="n">
-        <v>92430</v>
+        <v>92433</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137360125</v>
       </c>
       <c r="B3" t="n">
-        <v>79592</v>
+        <v>79595</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137360118</v>
       </c>
       <c r="B4" t="n">
-        <v>92155</v>
+        <v>92158</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137360132</v>
       </c>
       <c r="B5" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>137360126</v>
       </c>
       <c r="B6" t="n">
-        <v>92173</v>
+        <v>92176</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>137360129</v>
       </c>
       <c r="B7" t="n">
-        <v>92173</v>
+        <v>92176</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>137360122</v>
       </c>
       <c r="B8" t="n">
-        <v>92591</v>
+        <v>92594</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>137360119</v>
       </c>
       <c r="B9" t="n">
-        <v>83381</v>
+        <v>83384</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         <v>137360131</v>
       </c>
       <c r="B10" t="n">
-        <v>83509</v>
+        <v>83512</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1602,7 +1602,7 @@
         <v>137360127</v>
       </c>
       <c r="B11" t="n">
-        <v>92384</v>
+        <v>92387</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1704,7 +1704,7 @@
         <v>137360120</v>
       </c>
       <c r="B12" t="n">
-        <v>83504</v>
+        <v>83507</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1806,7 +1806,7 @@
         <v>137360124</v>
       </c>
       <c r="B13" t="n">
-        <v>83504</v>
+        <v>83507</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
         <v>137360123</v>
       </c>
       <c r="B14" t="n">
-        <v>83502</v>
+        <v>83505</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 35673-2026 artfynd.xlsx
+++ b/artfynd/A 35673-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137360121</v>
       </c>
       <c r="B2" t="n">
-        <v>92433</v>
+        <v>92435</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137360118</v>
       </c>
       <c r="B4" t="n">
-        <v>92158</v>
+        <v>92160</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137360132</v>
       </c>
       <c r="B5" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>137360126</v>
       </c>
       <c r="B6" t="n">
-        <v>92176</v>
+        <v>92178</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>137360129</v>
       </c>
       <c r="B7" t="n">
-        <v>92176</v>
+        <v>92178</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>137360122</v>
       </c>
       <c r="B8" t="n">
-        <v>92594</v>
+        <v>92596</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1602,7 +1602,7 @@
         <v>137360127</v>
       </c>
       <c r="B11" t="n">
-        <v>92387</v>
+        <v>92389</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 35673-2026 artfynd.xlsx
+++ b/artfynd/A 35673-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137360121</v>
       </c>
       <c r="B2" t="n">
-        <v>92435</v>
+        <v>92440</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137360125</v>
       </c>
       <c r="B3" t="n">
-        <v>79595</v>
+        <v>79600</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137360118</v>
       </c>
       <c r="B4" t="n">
-        <v>92160</v>
+        <v>92165</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137360132</v>
       </c>
       <c r="B5" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>137360126</v>
       </c>
       <c r="B6" t="n">
-        <v>92178</v>
+        <v>92183</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>137360129</v>
       </c>
       <c r="B7" t="n">
-        <v>92178</v>
+        <v>92183</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>137360122</v>
       </c>
       <c r="B8" t="n">
-        <v>92596</v>
+        <v>92601</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>137360119</v>
       </c>
       <c r="B9" t="n">
-        <v>83384</v>
+        <v>83389</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         <v>137360131</v>
       </c>
       <c r="B10" t="n">
-        <v>83512</v>
+        <v>83517</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1602,7 +1602,7 @@
         <v>137360127</v>
       </c>
       <c r="B11" t="n">
-        <v>92389</v>
+        <v>92394</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1704,7 +1704,7 @@
         <v>137360120</v>
       </c>
       <c r="B12" t="n">
-        <v>83507</v>
+        <v>83512</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1806,7 +1806,7 @@
         <v>137360124</v>
       </c>
       <c r="B13" t="n">
-        <v>83507</v>
+        <v>83512</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
         <v>137360123</v>
       </c>
       <c r="B14" t="n">
-        <v>83505</v>
+        <v>83510</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 35673-2026 artfynd.xlsx
+++ b/artfynd/A 35673-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137360121</v>
       </c>
       <c r="B2" t="n">
-        <v>92440</v>
+        <v>92452</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137360125</v>
       </c>
       <c r="B3" t="n">
-        <v>79600</v>
+        <v>79611</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137360118</v>
       </c>
       <c r="B4" t="n">
-        <v>92165</v>
+        <v>92177</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137360132</v>
       </c>
       <c r="B5" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>137360126</v>
       </c>
       <c r="B6" t="n">
-        <v>92183</v>
+        <v>92195</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>137360129</v>
       </c>
       <c r="B7" t="n">
-        <v>92183</v>
+        <v>92195</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>137360122</v>
       </c>
       <c r="B8" t="n">
-        <v>92601</v>
+        <v>92613</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>137360119</v>
       </c>
       <c r="B9" t="n">
-        <v>83389</v>
+        <v>83400</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         <v>137360131</v>
       </c>
       <c r="B10" t="n">
-        <v>83517</v>
+        <v>83528</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1602,7 +1602,7 @@
         <v>137360127</v>
       </c>
       <c r="B11" t="n">
-        <v>92394</v>
+        <v>92406</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1704,7 +1704,7 @@
         <v>137360120</v>
       </c>
       <c r="B12" t="n">
-        <v>83512</v>
+        <v>83523</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1806,7 +1806,7 @@
         <v>137360124</v>
       </c>
       <c r="B13" t="n">
-        <v>83512</v>
+        <v>83523</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
         <v>137360123</v>
       </c>
       <c r="B14" t="n">
-        <v>83510</v>
+        <v>83521</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 35673-2026 artfynd.xlsx
+++ b/artfynd/A 35673-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137360121</v>
       </c>
       <c r="B2" t="n">
-        <v>92452</v>
+        <v>92453</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137360125</v>
       </c>
       <c r="B3" t="n">
-        <v>79611</v>
+        <v>79612</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137360118</v>
       </c>
       <c r="B4" t="n">
-        <v>92177</v>
+        <v>92178</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137360132</v>
       </c>
       <c r="B5" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>137360126</v>
       </c>
       <c r="B6" t="n">
-        <v>92195</v>
+        <v>92196</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>137360129</v>
       </c>
       <c r="B7" t="n">
-        <v>92195</v>
+        <v>92196</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>137360122</v>
       </c>
       <c r="B8" t="n">
-        <v>92613</v>
+        <v>92614</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>137360119</v>
       </c>
       <c r="B9" t="n">
-        <v>83400</v>
+        <v>83401</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         <v>137360131</v>
       </c>
       <c r="B10" t="n">
-        <v>83528</v>
+        <v>83529</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1602,7 +1602,7 @@
         <v>137360127</v>
       </c>
       <c r="B11" t="n">
-        <v>92406</v>
+        <v>92407</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1704,7 +1704,7 @@
         <v>137360120</v>
       </c>
       <c r="B12" t="n">
-        <v>83523</v>
+        <v>83524</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1806,7 +1806,7 @@
         <v>137360124</v>
       </c>
       <c r="B13" t="n">
-        <v>83523</v>
+        <v>83524</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
         <v>137360123</v>
       </c>
       <c r="B14" t="n">
-        <v>83521</v>
+        <v>83522</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 35673-2026 artfynd.xlsx
+++ b/artfynd/A 35673-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137360121</v>
       </c>
       <c r="B2" t="n">
-        <v>92453</v>
+        <v>92456</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137360125</v>
       </c>
       <c r="B3" t="n">
-        <v>79612</v>
+        <v>79614</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137360118</v>
       </c>
       <c r="B4" t="n">
-        <v>92178</v>
+        <v>92181</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137360132</v>
       </c>
       <c r="B5" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>137360126</v>
       </c>
       <c r="B6" t="n">
-        <v>92196</v>
+        <v>92199</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>137360129</v>
       </c>
       <c r="B7" t="n">
-        <v>92196</v>
+        <v>92199</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>137360122</v>
       </c>
       <c r="B8" t="n">
-        <v>92614</v>
+        <v>92617</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>137360119</v>
       </c>
       <c r="B9" t="n">
-        <v>83401</v>
+        <v>83403</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         <v>137360131</v>
       </c>
       <c r="B10" t="n">
-        <v>83529</v>
+        <v>83531</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1602,7 +1602,7 @@
         <v>137360127</v>
       </c>
       <c r="B11" t="n">
-        <v>92407</v>
+        <v>92410</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1704,7 +1704,7 @@
         <v>137360120</v>
       </c>
       <c r="B12" t="n">
-        <v>83524</v>
+        <v>83526</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1806,7 +1806,7 @@
         <v>137360124</v>
       </c>
       <c r="B13" t="n">
-        <v>83524</v>
+        <v>83526</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
         <v>137360123</v>
       </c>
       <c r="B14" t="n">
-        <v>83522</v>
+        <v>83524</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 35673-2026 artfynd.xlsx
+++ b/artfynd/A 35673-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137360121</v>
       </c>
       <c r="B2" t="n">
-        <v>92456</v>
+        <v>92460</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137360125</v>
       </c>
       <c r="B3" t="n">
-        <v>79614</v>
+        <v>79618</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137360118</v>
       </c>
       <c r="B4" t="n">
-        <v>92181</v>
+        <v>92185</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137360132</v>
       </c>
       <c r="B5" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>137360126</v>
       </c>
       <c r="B6" t="n">
-        <v>92199</v>
+        <v>92203</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>137360129</v>
       </c>
       <c r="B7" t="n">
-        <v>92199</v>
+        <v>92203</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>137360122</v>
       </c>
       <c r="B8" t="n">
-        <v>92617</v>
+        <v>92621</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>137360119</v>
       </c>
       <c r="B9" t="n">
-        <v>83403</v>
+        <v>83407</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         <v>137360131</v>
       </c>
       <c r="B10" t="n">
-        <v>83531</v>
+        <v>83535</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1602,7 +1602,7 @@
         <v>137360127</v>
       </c>
       <c r="B11" t="n">
-        <v>92410</v>
+        <v>92414</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1704,7 +1704,7 @@
         <v>137360120</v>
       </c>
       <c r="B12" t="n">
-        <v>83526</v>
+        <v>83530</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1806,7 +1806,7 @@
         <v>137360124</v>
       </c>
       <c r="B13" t="n">
-        <v>83526</v>
+        <v>83530</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
         <v>137360123</v>
       </c>
       <c r="B14" t="n">
-        <v>83524</v>
+        <v>83528</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
